--- a/artfynd/A 6475-2025 artfynd.xlsx
+++ b/artfynd/A 6475-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122600065</v>
+        <v>122600072</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
+        <v>91242</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577008</v>
+        <v>577003</v>
       </c>
       <c r="R2" t="n">
-        <v>6415644</v>
+        <v>6415608</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,11 +762,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Få.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122600072</v>
+        <v>122600065</v>
       </c>
       <c r="B3" t="n">
-        <v>91242</v>
+        <v>98237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,38 +801,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577003</v>
+        <v>577008</v>
       </c>
       <c r="R3" t="n">
-        <v>6415608</v>
+        <v>6415644</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,6 +873,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Få.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 6475-2025 artfynd.xlsx
+++ b/artfynd/A 6475-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122600072</v>
+        <v>122600065</v>
       </c>
       <c r="B2" t="n">
-        <v>91242</v>
+        <v>98240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577003</v>
+        <v>577008</v>
       </c>
       <c r="R2" t="n">
-        <v>6415608</v>
+        <v>6415644</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Få.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122600065</v>
+        <v>122600080</v>
       </c>
       <c r="B3" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,35 +803,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577008</v>
+        <v>577078</v>
       </c>
       <c r="R3" t="n">
-        <v>6415644</v>
+        <v>6415529</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,18 +877,12 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Få.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122600080</v>
+        <v>122600072</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>91243</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,35 +913,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -953,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577078</v>
+        <v>577003</v>
       </c>
       <c r="R4" t="n">
-        <v>6415529</v>
+        <v>6415608</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,6 +996,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6475-2025 artfynd.xlsx
+++ b/artfynd/A 6475-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122600065</v>
       </c>
       <c r="B2" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>122600080</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>122600072</v>
       </c>
       <c r="B4" t="n">
-        <v>91243</v>
+        <v>91244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 6475-2025 artfynd.xlsx
+++ b/artfynd/A 6475-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122600065</v>
+        <v>122600072</v>
       </c>
       <c r="B2" t="n">
-        <v>98241</v>
+        <v>91247</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577008</v>
+        <v>577003</v>
       </c>
       <c r="R2" t="n">
-        <v>6415644</v>
+        <v>6415608</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,11 +762,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Få.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -901,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122600072</v>
+        <v>122600065</v>
       </c>
       <c r="B4" t="n">
-        <v>91244</v>
+        <v>98244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,38 +911,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577003</v>
+        <v>577008</v>
       </c>
       <c r="R4" t="n">
-        <v>6415608</v>
+        <v>6415644</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,6 +983,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Få.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 6475-2025 artfynd.xlsx
+++ b/artfynd/A 6475-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1013,6 +1013,1468 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122761530</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91348</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 6475, Oxebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>577014</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6415622</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122761584</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91348</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 6475, Oxebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>576995</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6415624</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122761497</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98345</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 6475, Oxebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>577019</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6415572</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122761659</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98345</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 6475, Oxebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>576987</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6415563</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122761556</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98345</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 6475, Oxebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>577019</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6415645</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122761567</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98345</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 6475, Oxebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>577007</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6415657</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122761614</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90938</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 6475, Oxebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>576990</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6415592</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Mkt på rätt klen granlåga</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122761626</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57493</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 6475, Oxebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>576990</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6415592</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hack på ulltickelågan</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122761574</v>
+      </c>
+      <c r="B13" t="n">
+        <v>110270</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 6475, Oxebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>577026</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6415675</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På marken på 3 ställen</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122761550</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98345</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A 6475, Oxebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>577004</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6415654</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122761512</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98345</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>A 6475, Oxebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>577035</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6415577</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122761643</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98345</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 6475, Oxebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>576968</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6415565</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122761492</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98345</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>A 6475, Oxebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>577020</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6415565</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6475-2025 artfynd.xlsx
+++ b/artfynd/A 6475-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122600072</v>
+        <v>122600080</v>
       </c>
       <c r="B2" t="n">
-        <v>91247</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577003</v>
+        <v>577078</v>
       </c>
       <c r="R2" t="n">
-        <v>6415608</v>
+        <v>6415529</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122600080</v>
+        <v>122600065</v>
       </c>
       <c r="B3" t="n">
-        <v>57400</v>
+        <v>98347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,35 +797,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577078</v>
+        <v>577008</v>
       </c>
       <c r="R3" t="n">
-        <v>6415529</v>
+        <v>6415644</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,12 +871,18 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Få.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122600065</v>
+        <v>122600072</v>
       </c>
       <c r="B4" t="n">
-        <v>98244</v>
+        <v>91350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,35 +913,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577008</v>
+        <v>577003</v>
       </c>
       <c r="R4" t="n">
-        <v>6415644</v>
+        <v>6415608</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,11 +988,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Få.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122761530</v>
+        <v>122761497</v>
       </c>
       <c r="B5" t="n">
-        <v>91348</v>
+        <v>98347</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,38 +1027,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577014</v>
+        <v>577019</v>
       </c>
       <c r="R5" t="n">
-        <v>6415622</v>
+        <v>6415572</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122761584</v>
+        <v>122761556</v>
       </c>
       <c r="B6" t="n">
-        <v>91348</v>
+        <v>98347</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,38 +1138,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576995</v>
+        <v>577019</v>
       </c>
       <c r="R6" t="n">
-        <v>6415624</v>
+        <v>6415645</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122761497</v>
+        <v>122761614</v>
       </c>
       <c r="B7" t="n">
-        <v>98345</v>
+        <v>90940</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,35 +1249,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1291,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577019</v>
+        <v>576990</v>
       </c>
       <c r="R7" t="n">
-        <v>6415572</v>
+        <v>6415592</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,6 +1324,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Mkt på rätt klen granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122761659</v>
+        <v>122761584</v>
       </c>
       <c r="B8" t="n">
-        <v>98345</v>
+        <v>91350</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,35 +1368,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1402,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576987</v>
+        <v>576995</v>
       </c>
       <c r="R8" t="n">
-        <v>6415563</v>
+        <v>6415624</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122761556</v>
+        <v>122761626</v>
       </c>
       <c r="B9" t="n">
-        <v>98345</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,35 +1482,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1513,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577019</v>
+        <v>576990</v>
       </c>
       <c r="R9" t="n">
-        <v>6415645</v>
+        <v>6415592</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,13 +1556,17 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hack på ulltickelågan</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1576,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122761567</v>
+        <v>122761659</v>
       </c>
       <c r="B10" t="n">
-        <v>98345</v>
+        <v>98347</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1624,10 +1633,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577007</v>
+        <v>576987</v>
       </c>
       <c r="R10" t="n">
-        <v>6415657</v>
+        <v>6415563</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122761614</v>
+        <v>122761643</v>
       </c>
       <c r="B11" t="n">
-        <v>90938</v>
+        <v>98347</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,38 +1708,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1738,10 +1744,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576990</v>
+        <v>576968</v>
       </c>
       <c r="R11" t="n">
-        <v>6415592</v>
+        <v>6415565</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1774,11 +1780,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Mkt på rätt klen granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,10 +1807,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122761626</v>
+        <v>122761530</v>
       </c>
       <c r="B12" t="n">
-        <v>57493</v>
+        <v>91350</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1818,35 +1819,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1854,10 +1858,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576990</v>
+        <v>577014</v>
       </c>
       <c r="R12" t="n">
-        <v>6415592</v>
+        <v>6415622</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,17 +1896,13 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hack på ulltickelågan</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1921,10 +1921,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122761574</v>
+        <v>122761512</v>
       </c>
       <c r="B13" t="n">
-        <v>110270</v>
+        <v>98347</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,29 +1933,33 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219677</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1965,10 +1969,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577026</v>
+        <v>577035</v>
       </c>
       <c r="R13" t="n">
-        <v>6415675</v>
+        <v>6415577</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,11 +2005,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På marken på 3 ställen</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,7 +2035,7 @@
         <v>122761550</v>
       </c>
       <c r="B14" t="n">
-        <v>98345</v>
+        <v>98347</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2144,10 +2143,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122761512</v>
+        <v>122761492</v>
       </c>
       <c r="B15" t="n">
-        <v>98345</v>
+        <v>98347</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2192,10 +2191,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577035</v>
+        <v>577020</v>
       </c>
       <c r="R15" t="n">
-        <v>6415577</v>
+        <v>6415565</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2255,10 +2254,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122761643</v>
+        <v>122761567</v>
       </c>
       <c r="B16" t="n">
-        <v>98345</v>
+        <v>98347</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,10 +2302,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576968</v>
+        <v>577007</v>
       </c>
       <c r="R16" t="n">
-        <v>6415565</v>
+        <v>6415657</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2366,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122761492</v>
+        <v>122761574</v>
       </c>
       <c r="B17" t="n">
-        <v>98345</v>
+        <v>110272</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2378,33 +2377,29 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2414,10 +2409,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577020</v>
+        <v>577026</v>
       </c>
       <c r="R17" t="n">
-        <v>6415565</v>
+        <v>6415675</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2450,6 +2445,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På marken på 3 ställen</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 6475-2025 artfynd.xlsx
+++ b/artfynd/A 6475-2025 artfynd.xlsx
@@ -1807,10 +1807,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122761530</v>
+        <v>122761512</v>
       </c>
       <c r="B12" t="n">
-        <v>91350</v>
+        <v>98347</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1819,38 +1819,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1858,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577014</v>
+        <v>577035</v>
       </c>
       <c r="R12" t="n">
-        <v>6415622</v>
+        <v>6415577</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1921,10 +1918,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122761512</v>
+        <v>122761530</v>
       </c>
       <c r="B13" t="n">
-        <v>98347</v>
+        <v>91350</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,35 +1930,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577035</v>
+        <v>577014</v>
       </c>
       <c r="R13" t="n">
-        <v>6415577</v>
+        <v>6415622</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 6475-2025 artfynd.xlsx
+++ b/artfynd/A 6475-2025 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122761497</v>
+        <v>122761614</v>
       </c>
       <c r="B5" t="n">
-        <v>98347</v>
+        <v>90944</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,35 +1027,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1063,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577019</v>
+        <v>576990</v>
       </c>
       <c r="R5" t="n">
-        <v>6415572</v>
+        <v>6415592</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,6 +1102,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mkt på rätt klen granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122761556</v>
+        <v>122761643</v>
       </c>
       <c r="B6" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577019</v>
+        <v>576968</v>
       </c>
       <c r="R6" t="n">
-        <v>6415645</v>
+        <v>6415565</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122761614</v>
+        <v>122761512</v>
       </c>
       <c r="B7" t="n">
-        <v>90940</v>
+        <v>98355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,38 +1257,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1288,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576990</v>
+        <v>577035</v>
       </c>
       <c r="R7" t="n">
-        <v>6415592</v>
+        <v>6415577</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,11 +1329,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Mkt på rätt klen granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122761584</v>
+        <v>122761626</v>
       </c>
       <c r="B8" t="n">
-        <v>91350</v>
+        <v>57494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,38 +1368,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1407,10 +1404,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576995</v>
+        <v>576990</v>
       </c>
       <c r="R8" t="n">
-        <v>6415624</v>
+        <v>6415592</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,13 +1442,17 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hack på ulltickelågan</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1470,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122761626</v>
+        <v>122761497</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>98355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,35 +1483,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1518,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576990</v>
+        <v>577019</v>
       </c>
       <c r="R9" t="n">
-        <v>6415592</v>
+        <v>6415572</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,17 +1557,13 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hack på ulltickelågan</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1585,10 +1582,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122761659</v>
+        <v>122761574</v>
       </c>
       <c r="B10" t="n">
-        <v>98347</v>
+        <v>110280</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,33 +1594,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1633,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576987</v>
+        <v>577026</v>
       </c>
       <c r="R10" t="n">
-        <v>6415563</v>
+        <v>6415675</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,6 +1662,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På marken på 3 ställen</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1694,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122761643</v>
+        <v>122761550</v>
       </c>
       <c r="B11" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576968</v>
+        <v>577004</v>
       </c>
       <c r="R11" t="n">
-        <v>6415565</v>
+        <v>6415654</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122761512</v>
+        <v>122761556</v>
       </c>
       <c r="B12" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,10 +1853,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577035</v>
+        <v>577019</v>
       </c>
       <c r="R12" t="n">
-        <v>6415577</v>
+        <v>6415645</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122761530</v>
+        <v>122761492</v>
       </c>
       <c r="B13" t="n">
-        <v>91350</v>
+        <v>98355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1930,38 +1928,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1969,10 +1964,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577014</v>
+        <v>577020</v>
       </c>
       <c r="R13" t="n">
-        <v>6415622</v>
+        <v>6415565</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2032,10 +2027,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122761550</v>
+        <v>122761530</v>
       </c>
       <c r="B14" t="n">
-        <v>98347</v>
+        <v>91354</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,35 +2039,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2080,10 +2078,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577004</v>
+        <v>577014</v>
       </c>
       <c r="R14" t="n">
-        <v>6415654</v>
+        <v>6415622</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2143,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122761492</v>
+        <v>122761567</v>
       </c>
       <c r="B15" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2191,10 +2189,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577020</v>
+        <v>577007</v>
       </c>
       <c r="R15" t="n">
-        <v>6415565</v>
+        <v>6415657</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2254,10 +2252,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122761567</v>
+        <v>122761584</v>
       </c>
       <c r="B16" t="n">
-        <v>98347</v>
+        <v>91354</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2266,35 +2264,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2302,10 +2303,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577007</v>
+        <v>576995</v>
       </c>
       <c r="R16" t="n">
-        <v>6415657</v>
+        <v>6415624</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2365,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122761574</v>
+        <v>122761659</v>
       </c>
       <c r="B17" t="n">
-        <v>110272</v>
+        <v>98355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2377,29 +2378,33 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219677</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2409,10 +2414,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577026</v>
+        <v>576987</v>
       </c>
       <c r="R17" t="n">
-        <v>6415675</v>
+        <v>6415563</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2445,11 +2450,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På marken på 3 ställen</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 6475-2025 artfynd.xlsx
+++ b/artfynd/A 6475-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122600080</v>
+        <v>122600065</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>98355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577078</v>
+        <v>577008</v>
       </c>
       <c r="R2" t="n">
-        <v>6415529</v>
+        <v>6415644</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,12 +761,18 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Få.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122600065</v>
+        <v>122600072</v>
       </c>
       <c r="B3" t="n">
-        <v>98347</v>
+        <v>91354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,35 +803,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577008</v>
+        <v>577003</v>
       </c>
       <c r="R3" t="n">
-        <v>6415644</v>
+        <v>6415608</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,11 +878,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Få.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122600072</v>
+        <v>122600080</v>
       </c>
       <c r="B4" t="n">
-        <v>91350</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,38 +917,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577003</v>
+        <v>577078</v>
       </c>
       <c r="R4" t="n">
-        <v>6415608</v>
+        <v>6415529</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +997,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122761584</v>
+        <v>122761659</v>
       </c>
       <c r="B16" t="n">
-        <v>91354</v>
+        <v>98355</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,38 +2264,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2303,10 +2300,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576995</v>
+        <v>576987</v>
       </c>
       <c r="R16" t="n">
-        <v>6415624</v>
+        <v>6415563</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2366,10 +2363,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122761659</v>
+        <v>122761584</v>
       </c>
       <c r="B17" t="n">
-        <v>98355</v>
+        <v>91354</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2378,35 +2375,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576987</v>
+        <v>576995</v>
       </c>
       <c r="R17" t="n">
-        <v>6415563</v>
+        <v>6415624</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 6475-2025 artfynd.xlsx
+++ b/artfynd/A 6475-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122600065</v>
+        <v>122600072</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
+        <v>91354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577008</v>
+        <v>577003</v>
       </c>
       <c r="R2" t="n">
-        <v>6415644</v>
+        <v>6415608</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,11 +762,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Få.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122600072</v>
+        <v>122600065</v>
       </c>
       <c r="B3" t="n">
-        <v>91354</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,38 +801,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577003</v>
+        <v>577008</v>
       </c>
       <c r="R3" t="n">
-        <v>6415608</v>
+        <v>6415644</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,6 +873,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Få.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122761614</v>
+        <v>122761530</v>
       </c>
       <c r="B5" t="n">
-        <v>90944</v>
+        <v>91354</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,35 +1027,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576990</v>
+        <v>577014</v>
       </c>
       <c r="R5" t="n">
-        <v>6415592</v>
+        <v>6415622</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,11 +1102,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mkt på rätt klen granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,7 +1129,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122761643</v>
+        <v>122761492</v>
       </c>
       <c r="B6" t="n">
         <v>98355</v>
@@ -1182,7 +1177,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576968</v>
+        <v>577020</v>
       </c>
       <c r="R6" t="n">
         <v>6415565</v>
@@ -1245,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122761512</v>
+        <v>122761574</v>
       </c>
       <c r="B7" t="n">
-        <v>98355</v>
+        <v>110280</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,33 +1252,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1293,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577035</v>
+        <v>577026</v>
       </c>
       <c r="R7" t="n">
-        <v>6415577</v>
+        <v>6415675</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,6 +1320,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På marken på 3 ställen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1471,7 +1467,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122761497</v>
+        <v>122761567</v>
       </c>
       <c r="B9" t="n">
         <v>98355</v>
@@ -1519,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577019</v>
+        <v>577007</v>
       </c>
       <c r="R9" t="n">
-        <v>6415572</v>
+        <v>6415657</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1582,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122761574</v>
+        <v>122761584</v>
       </c>
       <c r="B10" t="n">
-        <v>110280</v>
+        <v>91354</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,27 +1594,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219677</v>
+        <v>5420</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1626,10 +1629,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577026</v>
+        <v>576995</v>
       </c>
       <c r="R10" t="n">
-        <v>6415675</v>
+        <v>6415624</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,11 +1665,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På marken på 3 ställen</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,7 +1692,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122761550</v>
+        <v>122761643</v>
       </c>
       <c r="B11" t="n">
         <v>98355</v>
@@ -1742,10 +1740,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577004</v>
+        <v>576968</v>
       </c>
       <c r="R11" t="n">
-        <v>6415654</v>
+        <v>6415565</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1805,7 +1803,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122761556</v>
+        <v>122761497</v>
       </c>
       <c r="B12" t="n">
         <v>98355</v>
@@ -1856,7 +1854,7 @@
         <v>577019</v>
       </c>
       <c r="R12" t="n">
-        <v>6415645</v>
+        <v>6415572</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1916,7 +1914,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122761492</v>
+        <v>122761550</v>
       </c>
       <c r="B13" t="n">
         <v>98355</v>
@@ -1964,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577020</v>
+        <v>577004</v>
       </c>
       <c r="R13" t="n">
-        <v>6415565</v>
+        <v>6415654</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2027,10 +2025,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122761530</v>
+        <v>122761659</v>
       </c>
       <c r="B14" t="n">
-        <v>91354</v>
+        <v>98355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2039,38 +2037,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2078,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577014</v>
+        <v>576987</v>
       </c>
       <c r="R14" t="n">
-        <v>6415622</v>
+        <v>6415563</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2141,7 +2136,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122761567</v>
+        <v>122761512</v>
       </c>
       <c r="B15" t="n">
         <v>98355</v>
@@ -2189,10 +2184,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577007</v>
+        <v>577035</v>
       </c>
       <c r="R15" t="n">
-        <v>6415657</v>
+        <v>6415577</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2252,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122761659</v>
+        <v>122761614</v>
       </c>
       <c r="B16" t="n">
-        <v>98355</v>
+        <v>90944</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,35 +2259,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2300,10 +2298,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576987</v>
+        <v>576990</v>
       </c>
       <c r="R16" t="n">
-        <v>6415563</v>
+        <v>6415592</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2336,6 +2334,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Mkt på rätt klen granlåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2363,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122761584</v>
+        <v>122761556</v>
       </c>
       <c r="B17" t="n">
-        <v>91354</v>
+        <v>98355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2375,38 +2378,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576995</v>
+        <v>577019</v>
       </c>
       <c r="R17" t="n">
-        <v>6415624</v>
+        <v>6415645</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 6475-2025 artfynd.xlsx
+++ b/artfynd/A 6475-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122600072</v>
+        <v>122600080</v>
       </c>
       <c r="B2" t="n">
-        <v>91354</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577003</v>
+        <v>577078</v>
       </c>
       <c r="R2" t="n">
-        <v>6415608</v>
+        <v>6415529</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,7 +788,7 @@
         <v>122600065</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -905,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122600080</v>
+        <v>122600072</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>91354</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,35 +913,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -953,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577078</v>
+        <v>577003</v>
       </c>
       <c r="R4" t="n">
-        <v>6415529</v>
+        <v>6415608</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,6 +996,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1015,7 +1015,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122761530</v>
+        <v>122761584</v>
       </c>
       <c r="B5" t="n">
         <v>91354</v>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577014</v>
+        <v>576995</v>
       </c>
       <c r="R5" t="n">
-        <v>6415622</v>
+        <v>6415624</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122761492</v>
+        <v>122761626</v>
       </c>
       <c r="B6" t="n">
-        <v>98355</v>
+        <v>57494</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,35 +1141,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577020</v>
+        <v>576990</v>
       </c>
       <c r="R6" t="n">
-        <v>6415565</v>
+        <v>6415592</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,13 +1215,17 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack på ulltickelågan</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1240,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122761574</v>
+        <v>122761556</v>
       </c>
       <c r="B7" t="n">
-        <v>110280</v>
+        <v>98357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,29 +1256,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219677</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1284,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577026</v>
+        <v>577019</v>
       </c>
       <c r="R7" t="n">
-        <v>6415675</v>
+        <v>6415645</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,11 +1328,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På marken på 3 ställen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122761626</v>
+        <v>122761659</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>98357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,35 +1367,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1400,10 +1403,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576990</v>
+        <v>576987</v>
       </c>
       <c r="R8" t="n">
-        <v>6415592</v>
+        <v>6415563</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,17 +1441,13 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hack på ulltickelågan</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1467,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122761567</v>
+        <v>122761512</v>
       </c>
       <c r="B9" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577007</v>
+        <v>577035</v>
       </c>
       <c r="R9" t="n">
-        <v>6415657</v>
+        <v>6415577</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,10 +1577,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122761584</v>
+        <v>122761643</v>
       </c>
       <c r="B10" t="n">
-        <v>91354</v>
+        <v>98357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,38 +1589,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1629,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576995</v>
+        <v>576968</v>
       </c>
       <c r="R10" t="n">
-        <v>6415624</v>
+        <v>6415565</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122761643</v>
+        <v>122761497</v>
       </c>
       <c r="B11" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576968</v>
+        <v>577019</v>
       </c>
       <c r="R11" t="n">
-        <v>6415565</v>
+        <v>6415572</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1803,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122761497</v>
+        <v>122761550</v>
       </c>
       <c r="B12" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1851,10 +1847,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577019</v>
+        <v>577004</v>
       </c>
       <c r="R12" t="n">
-        <v>6415572</v>
+        <v>6415654</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122761550</v>
+        <v>122761492</v>
       </c>
       <c r="B13" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,10 +1958,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577004</v>
+        <v>577020</v>
       </c>
       <c r="R13" t="n">
-        <v>6415654</v>
+        <v>6415565</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,10 +2021,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122761659</v>
+        <v>122761567</v>
       </c>
       <c r="B14" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2073,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576987</v>
+        <v>577007</v>
       </c>
       <c r="R14" t="n">
-        <v>6415563</v>
+        <v>6415657</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2136,10 +2132,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122761512</v>
+        <v>122761530</v>
       </c>
       <c r="B15" t="n">
-        <v>98355</v>
+        <v>91354</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2148,35 +2144,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2184,10 +2183,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577035</v>
+        <v>577014</v>
       </c>
       <c r="R15" t="n">
-        <v>6415577</v>
+        <v>6415622</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2247,10 +2246,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122761614</v>
+        <v>122761574</v>
       </c>
       <c r="B16" t="n">
-        <v>90944</v>
+        <v>110282</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,38 +2258,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>219677</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2298,10 +2290,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576990</v>
+        <v>577026</v>
       </c>
       <c r="R16" t="n">
-        <v>6415592</v>
+        <v>6415675</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2338,7 +2330,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Mkt på rätt klen granlåga</t>
+          <t>På marken på 3 ställen</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122761556</v>
+        <v>122761614</v>
       </c>
       <c r="B17" t="n">
-        <v>98355</v>
+        <v>90944</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2378,35 +2370,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2414,10 +2409,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577019</v>
+        <v>576990</v>
       </c>
       <c r="R17" t="n">
-        <v>6415645</v>
+        <v>6415592</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2450,6 +2445,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Mkt på rätt klen granlåga</t>
         </is>
       </c>
       <c r="AD17" t="b">
